--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N38_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N38_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>45.38606671916214</v>
+        <v>7.375235841863848</v>
       </c>
       <c r="D2" t="n">
-        <v>47.4988473982562</v>
+        <v>7.718562702216632</v>
       </c>
       <c r="E2" t="n">
-        <v>14.46633336962767</v>
+        <v>2.350779172564496</v>
       </c>
       <c r="F2" t="n">
-        <v>16.18708236466389</v>
+        <v>2.630400884257883</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>78.20534105160861</v>
+        <v>12.7083679208864</v>
       </c>
       <c r="D3" t="n">
-        <v>75.16648189186454</v>
+        <v>12.21455330742799</v>
       </c>
       <c r="E3" t="n">
-        <v>14.46633336962767</v>
+        <v>2.350779172564496</v>
       </c>
       <c r="F3" t="n">
-        <v>16.18708236466389</v>
+        <v>2.630400884257883</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.93513961802641</v>
+        <v>8.601960187929292</v>
       </c>
       <c r="D4" t="n">
-        <v>52.35756461676532</v>
+        <v>8.508104250224365</v>
       </c>
       <c r="E4" t="n">
-        <v>14.46633336962767</v>
+        <v>2.350779172564496</v>
       </c>
       <c r="F4" t="n">
-        <v>16.18708236466389</v>
+        <v>2.630400884257883</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>54.70453950328886</v>
+        <v>8.88948766928444</v>
       </c>
       <c r="D5" t="n">
-        <v>46.76804464589043</v>
+        <v>7.599807254957194</v>
       </c>
       <c r="E5" t="n">
-        <v>14.46633336962767</v>
+        <v>2.350779172564496</v>
       </c>
       <c r="F5" t="n">
-        <v>16.18708236466389</v>
+        <v>2.630400884257883</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>62.08695349539543</v>
+        <v>10.08912994300176</v>
       </c>
       <c r="D6" t="n">
-        <v>48.50773134253961</v>
+        <v>7.882506343162688</v>
       </c>
       <c r="E6" t="n">
-        <v>14.46633336962767</v>
+        <v>2.350779172564496</v>
       </c>
       <c r="F6" t="n">
-        <v>16.18708236466389</v>
+        <v>2.630400884257883</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>68.17516149187196</v>
+        <v>11.07846374242919</v>
       </c>
       <c r="D7" t="n">
-        <v>50.7140449671227</v>
+        <v>8.24103230715744</v>
       </c>
       <c r="E7" t="n">
-        <v>14.46633336962767</v>
+        <v>2.350779172564496</v>
       </c>
       <c r="F7" t="n">
-        <v>16.18708236466389</v>
+        <v>2.630400884257883</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>77.30474914722713</v>
+        <v>12.56202173642441</v>
       </c>
       <c r="D8" t="n">
-        <v>66.72705598181295</v>
+        <v>10.8431465970446</v>
       </c>
       <c r="E8" t="n">
-        <v>14.46633336962767</v>
+        <v>2.350779172564496</v>
       </c>
       <c r="F8" t="n">
-        <v>16.18708236466389</v>
+        <v>2.630400884257883</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.78005467154846</v>
+        <v>5.489258884126626</v>
       </c>
       <c r="D9" t="n">
-        <v>15.94521871910197</v>
+        <v>2.591098041854071</v>
       </c>
       <c r="E9" t="n">
-        <v>14.46633336962767</v>
+        <v>2.350779172564496</v>
       </c>
       <c r="F9" t="n">
-        <v>16.18708236466389</v>
+        <v>2.630400884257883</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
